--- a/samples/spreadsheets/项目进度表.xlsx
+++ b/samples/spreadsheets/项目进度表.xlsx
@@ -442,7 +442,7 @@
         <v>100%</v>
       </c>
       <c r="D2" t="str">
-        <v>张三</v>
+        <v>陈强</v>
       </c>
       <c r="E2" t="str">
         <v>2026-06-16</v>
@@ -465,7 +465,7 @@
         <v>100%</v>
       </c>
       <c r="D3" t="str">
-        <v>王五</v>
+        <v>赵丽</v>
       </c>
       <c r="E3" t="str">
         <v>2026-06-16</v>
@@ -488,7 +488,7 @@
         <v>100%</v>
       </c>
       <c r="D4" t="str">
-        <v>李四</v>
+        <v>刘伟</v>
       </c>
       <c r="E4" t="str">
         <v>2026-06-16</v>
@@ -511,7 +511,7 @@
         <v>100%</v>
       </c>
       <c r="D5" t="str">
-        <v>李四</v>
+        <v>刘伟</v>
       </c>
       <c r="E5" t="str">
         <v>2026-06-16</v>
@@ -534,7 +534,7 @@
         <v>100%</v>
       </c>
       <c r="D6" t="str">
-        <v>王五</v>
+        <v>赵丽</v>
       </c>
       <c r="E6" t="str">
         <v>2026-06-16</v>
@@ -557,7 +557,7 @@
         <v>80%</v>
       </c>
       <c r="D7" t="str">
-        <v>赵六</v>
+        <v>杨飞</v>
       </c>
       <c r="E7" t="str">
         <v>2026-06-16</v>
@@ -580,7 +580,7 @@
         <v>100%</v>
       </c>
       <c r="D8" t="str">
-        <v>张三、李四</v>
+        <v>陈强、刘伟</v>
       </c>
       <c r="E8" t="str">
         <v>2026-06-16</v>
@@ -603,7 +603,7 @@
         <v>0%</v>
       </c>
       <c r="D9" t="str">
-        <v>张三、李四</v>
+        <v>陈强、刘伟</v>
       </c>
       <c r="E9" t="str">
         <v>2026-06-23</v>
@@ -626,7 +626,7 @@
         <v>100%</v>
       </c>
       <c r="D10" t="str">
-        <v>王五</v>
+        <v>赵丽</v>
       </c>
       <c r="E10" t="str">
         <v>2026-06-18</v>
@@ -649,7 +649,7 @@
         <v>100%</v>
       </c>
       <c r="D11" t="str">
-        <v>李四</v>
+        <v>刘伟</v>
       </c>
       <c r="E11" t="str">
         <v>2026-06-19</v>
